--- a/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/07,26/28,07,26 ПОКОМ КИ/машины ПОКОМ КИ.xlsx
+++ b/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/07,26/28,07,26 ПОКОМ КИ/машины ПОКОМ КИ.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты ПОКОМ КИ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\ПОКОМ\филиалы НВ\07,26\28,07,26 ПОКОМ КИ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55F8326B-330B-4441-AAC2-93226B119665}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B74CCA55-E525-49CA-BF06-87EEBDF8C9E3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="32">
   <si>
     <t>Бердянск</t>
   </si>
@@ -2074,6 +2074,9 @@
       <c r="Z19" t="s">
         <v>30</v>
       </c>
+      <c r="AC19" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="20" spans="1:32" x14ac:dyDescent="0.25">
       <c r="W20">
